--- a/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
+++ b/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dairon Alonso\Desktop\App Streamlit-Prediccion\Streamlit\Plantillas\Nombre Clientes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8913F75-0173-473F-AC58-02FA41A07DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Hoja1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$C$41</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="74">
   <si>
     <t>Sold To</t>
   </si>
@@ -233,13 +242,15 @@
   </si>
   <si>
     <t>DROGUERIA MAYO S.R.L</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA FARMACEUTICA ECUATORIANA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -282,32 +293,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -318,10 +329,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -359,71 +370,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -451,7 +462,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -474,11 +485,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -487,13 +498,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -503,7 +514,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -512,7 +523,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -521,7 +532,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -529,10 +540,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -597,470 +608,594 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C82"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="79.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="49.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="11.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="3">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>100173503</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="3">
+    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>100173496</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="3">
+    <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>100173512</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="3">
+    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>100173495</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="3">
+    <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>100173090</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="3">
+    <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>100173513</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="3">
+    <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>100173510</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="3">
+    <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>100173499</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="3">
+    <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>100370268</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="3">
+    <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>100173500</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="3">
+    <row r="12" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>100173466</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="3">
+    <row r="13" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>100173467</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="3">
+    <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>100173530</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="3">
+    <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>100173502</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="3">
+    <row r="16" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>100174043</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="3">
+    <row r="17" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>100173527</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="3">
+    <row r="18" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>100173504</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="3">
+    <row r="19" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>100173509</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="3">
+    <row r="20" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>100174034</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="3">
+    <row r="21" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>100173508</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="3">
+    <row r="22" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>100174041</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="3">
+    <row r="23" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>100174039</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>42</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="3">
+    <row r="24" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>100276516</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
-      <c r="A25" s="3">
+    <row r="25" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>100178663</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
-      <c r="A26" s="3">
+    <row r="26" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>100173518</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="3">
+    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>100173522</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" t="s">
         <v>49</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="3">
+    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>100173459</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>51</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="3">
+    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>100178746</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="3">
+    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>100284233</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="3">
+    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>100173454</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="3">
+    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>100179133</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="3">
+    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>100174343</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" t="s">
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="3">
-        <v>100179133</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="3">
+    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>100184508</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B34" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C34" t="s">
         <v>61</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="3">
+    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>100184510</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B35" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C35" t="s">
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="3">
+    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>100184507</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B36" t="s">
         <v>64</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C36" t="s">
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="3">
+    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>100174337</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B37" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C37" t="s">
         <v>67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="3">
+    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>2029200</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B38" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C38" t="s">
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="3">
+    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>2032700</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B39" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C39" t="s">
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="3">
+    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>2072300</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B40" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C40" t="s">
         <v>72</v>
       </c>
     </row>
+    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>100174040</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:C41" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
+++ b/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dairon Alonso\Desktop\App Streamlit-Prediccion\Streamlit\Plantillas\Nombre Clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8913F75-0173-473F-AC58-02FA41A07DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61214349-5CB1-43F0-886F-2E9793F8FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1072,7 +1072,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42"/>
+      <c r="A42" s="4"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43"/>

--- a/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
+++ b/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dairon Alonso\Desktop\App Streamlit-Prediccion\Streamlit\Plantillas\Nombre Clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61214349-5CB1-43F0-886F-2E9793F8FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CD9035-D602-465A-B802-5276388907EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="83">
   <si>
     <t>Sold To</t>
   </si>
@@ -245,13 +245,40 @@
   </si>
   <si>
     <t>DISTRIBUIDORA FARMACEUTICA ECUATORIANA</t>
+  </si>
+  <si>
+    <t>DROGUERIA MAR DE JUFEC S.A.</t>
+  </si>
+  <si>
+    <t>DROGUERIA MAR DE JUFEC</t>
+  </si>
+  <si>
+    <t>DROGUERIA MAYO</t>
+  </si>
+  <si>
+    <t>DROGUERIA DEL SUD S.A.C.I.</t>
+  </si>
+  <si>
+    <t>DROGUERIA DEL SUD</t>
+  </si>
+  <si>
+    <t>DROG. MONROE AMERICANA</t>
+  </si>
+  <si>
+    <t>DROGUERÍA MONROE AMERICANA</t>
+  </si>
+  <si>
+    <t>SUIZO ARGENTINA S.A.</t>
+  </si>
+  <si>
+    <t>SUIZO ARGENTINA SA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +289,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -293,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -305,6 +338,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1072,19 +1108,59 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
+      <c r="A42" s="5">
+        <v>2059200</v>
+      </c>
+      <c r="B42" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43"/>
+      <c r="A43" s="5">
+        <v>2072300</v>
+      </c>
+      <c r="B43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44"/>
+      <c r="A44" s="5">
+        <v>2032500</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45"/>
+      <c r="A45" s="5">
+        <v>2023804</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46"/>
+      <c r="A46" s="5">
+        <v>2023700</v>
+      </c>
+      <c r="B46" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47"/>

--- a/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
+++ b/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dairon Alonso\Desktop\App Streamlit-Prediccion\Streamlit\Plantillas\Nombre Clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CD9035-D602-465A-B802-5276388907EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5F04DD-42E2-4803-8EEA-613B526C7CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
   <si>
     <t>Sold To</t>
   </si>
@@ -253,9 +253,6 @@
     <t>DROGUERIA MAR DE JUFEC</t>
   </si>
   <si>
-    <t>DROGUERIA MAYO</t>
-  </si>
-  <si>
     <t>DROGUERIA DEL SUD S.A.C.I.</t>
   </si>
   <si>
@@ -272,6 +269,24 @@
   </si>
   <si>
     <t>SUIZO ARGENTINA SA</t>
+  </si>
+  <si>
+    <t>SUPERTIENDAS Y DROGUERIAS OLIMPICA S.A.</t>
+  </si>
+  <si>
+    <t>OLIMPICA</t>
+  </si>
+  <si>
+    <t>UNION DE DROGUISTAS SAS - UNIDROGAS SAS</t>
+  </si>
+  <si>
+    <t>UNIDROGAS</t>
+  </si>
+  <si>
+    <t>ALIMENTOS POLAR COLOMBIA S.A.S.</t>
+  </si>
+  <si>
+    <t>POLAR</t>
   </si>
 </sst>
 </file>
@@ -648,7 +663,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="3" bestFit="1" customWidth="1"/>
@@ -667,466 +682,456 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>100173503</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>100173496</v>
+        <v>100173503</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>100173512</v>
+        <v>100173496</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>100173495</v>
+        <v>100173512</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>100173090</v>
+        <v>100173495</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>100173513</v>
+        <v>100173090</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>100173510</v>
+        <v>100173513</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>100173499</v>
+        <v>100173510</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>100370268</v>
+        <v>100173499</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>100173500</v>
+        <v>100370268</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>100173466</v>
+        <v>100173500</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>100173467</v>
+        <v>100173466</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>100173530</v>
+        <v>100173467</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>100173502</v>
+        <v>100173530</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>100174043</v>
+        <v>100173502</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>100173527</v>
+        <v>100174043</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>100173504</v>
+        <v>100173527</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>100173509</v>
+        <v>100173504</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>100174034</v>
+        <v>100173509</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>100173508</v>
+        <v>100174034</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>100174041</v>
+        <v>100173508</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>100174039</v>
+        <v>100174041</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>100276516</v>
+        <v>100174039</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>100178663</v>
+        <v>100276516</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>100173518</v>
+        <v>100178663</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>100173522</v>
+        <v>100173518</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>100173459</v>
+        <v>100173522</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>100178746</v>
+        <v>100173459</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>100284233</v>
+        <v>100178746</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>100173454</v>
+        <v>100284233</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>100179133</v>
+        <v>100173454</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>100174343</v>
+        <v>100179133</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>100184508</v>
+        <v>100174343</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>100184510</v>
+        <v>100184508</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>100184507</v>
+        <v>100184510</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>100174337</v>
+        <v>100184507</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>2029200</v>
+        <v>100174337</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>2032700</v>
+        <v>2029200</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
+        <v>2032700</v>
+      </c>
+      <c r="B40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>2072300</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>71</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
         <v>100174040</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>73</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>2059200</v>
-      </c>
-      <c r="B42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>2072300</v>
+        <v>2059200</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1134,10 +1139,10 @@
         <v>2032500</v>
       </c>
       <c r="B44" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" t="s">
         <v>77</v>
-      </c>
-      <c r="C44" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1145,10 +1150,10 @@
         <v>2023804</v>
       </c>
       <c r="B45" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" t="s">
         <v>79</v>
-      </c>
-      <c r="C45" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1156,64 +1161,88 @@
         <v>2023700</v>
       </c>
       <c r="B46" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" t="s">
         <v>81</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="B47" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47"/>
+      <c r="C47" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>100173449</v>
+      </c>
+      <c r="B48" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>100370270</v>
+      </c>
+      <c r="B49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
@@ -1270,8 +1299,32 @@
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82"/>
     </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C41" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C49" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
+++ b/Plantillas/Nombre Clientes/Nombre Clientes.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dairon Alonso\Desktop\App Streamlit-Prediccion\Streamlit\Plantillas\Nombre Clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5F04DD-42E2-4803-8EEA-613B526C7CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAE5375-8434-4572-8B42-764D39A714D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="6240" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$C$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$C$49</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="114">
   <si>
     <t>Sold To</t>
   </si>
@@ -287,13 +287,91 @@
   </si>
   <si>
     <t>POLAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORPORACION CEFA DE NICARAGUA S. A. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEFA DE NICARAGUA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DROGUERIA PROCONSUMO, S.A. DE C.V. </t>
+  </si>
+  <si>
+    <t>DROGUERIA PROCONSUMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscar Q. Renta Negrón, S. A. </t>
+  </si>
+  <si>
+    <t>Oscar Q. Renta Negrón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REPRICO, S.A. PANAMA </t>
+  </si>
+  <si>
+    <t>REPRICO, S.A</t>
+  </si>
+  <si>
+    <t>BODEGA FARMACEUTICA, S.A - BOFASA</t>
+  </si>
+  <si>
+    <t>BODEGA FARMACEUTICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEFA CENTRAL FARMACEUTICA , S.A. </t>
+  </si>
+  <si>
+    <t>CEFA CENTRAL FARMACEUTICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.IMBERTON, S.A. DE C.V. EL SALVADOR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.IMBERTON, S.A. </t>
+  </si>
+  <si>
+    <t>CALOX INTERNATIONAL C.A. -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALOX INTERNATIONAL </t>
+  </si>
+  <si>
+    <t>INRETAIL PHARMA S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INRETAIL PHARMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUIMIZA LTDA BOLIVIA </t>
+  </si>
+  <si>
+    <t>QUIMIZA LTDA</t>
+  </si>
+  <si>
+    <t>BRYDEN PI LIMITED - TRINIDAD Y TOBAGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRYDEN PI LIMITED </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDEX S. A. C. I. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDEX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MURRY S. A. </t>
+  </si>
+  <si>
+    <t>MURRY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +391,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -322,7 +421,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -337,11 +436,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -358,9 +473,19 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{66E049C9-CAED-4C41-9F2E-5CC6A15FF6B4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1201,43 +1326,147 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50"/>
+      <c r="A50" s="6">
+        <v>100282685</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51"/>
+      <c r="A51" s="6">
+        <v>100174337</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52"/>
+      <c r="A52" s="6">
+        <v>100184474</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53"/>
+      <c r="A53" s="6">
+        <v>100174305</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54"/>
+      <c r="A54" s="6">
+        <v>100179133</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55"/>
+      <c r="A55" s="6">
+        <v>100142307</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56"/>
+      <c r="A56" s="6">
+        <v>100142299</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57"/>
+      <c r="A57" s="6">
+        <v>100219811</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58"/>
+      <c r="A58" s="6">
+        <v>100249811</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59"/>
+      <c r="A59" s="6">
+        <v>100174339</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60"/>
+      <c r="A60" s="6">
+        <v>100174343</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61"/>
+      <c r="A61" s="6">
+        <v>100184508</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62"/>
+      <c r="A62" s="6">
+        <v>100184507</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63"/>
@@ -1324,7 +1553,7 @@
       <c r="A90"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C49" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>